--- a/output/2026-10-03_17_Malesia_Perlis_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-03_17_Malesia_Perlis_Impiantistica_aspirazione_industriale.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sede a Penang (area allargata, non a Perlis). Esistenza e contatti confermati via sito ufficiale.</t>
+          <t>Sede a Penang (area allargata, non a Perlis). Esistenza e contatti confermati via sito ufficiale. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -540,10 +540,9 @@
           <t>+60-98592095</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore/installatore regionale senza sede fissa a Perlis; confermato via sito ufficiale zabsi.com.</t>
+          <t>Distributore/installatore regionale senza sede fissa a Perlis; confermato via sito ufficiale zabsi.com. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +584,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Distributore regionale senza sede a Perlis, ha filiale a Penang. Confermato via sito ufficiale.</t>
+          <t>Distributore regionale senza sede a Perlis, ha filiale a Penang. Confermato via sito ufficiale. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -600,7 +599,6 @@
           <t>Vibran Engineering (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Petaling Jaya / Subang, Selangor</t>
@@ -611,8 +609,6 @@
           <t>Design, fabbricazione e installazione sistemi ventilazione/exhaust industriale, exhaust fan industriali (incl. settore palm oil), air pollution control</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Nessun sito web ufficiale reperito; esistenza confermata da directory aziendali (maukerja.my). Azienda storica dal 1983. Sede non a Perlis.</t>
@@ -620,7 +616,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -630,7 +626,6 @@
           <t>Kemac Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Kuala Lumpur</t>
@@ -641,11 +636,9 @@
           <t>Progettazione e fabbricazione bag filter dust collector, pulse jet dust collector, controllo polveri industriali</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nessun sito web/contatti diretti reperiti; esistenza confermata da directory aziendali (emis.cn, maukerja.my). Azienda storica dal 1978. Sede non a Perlis.</t>
+          <t>Nessun sito web/contatti diretti reperiti; esistenza confermata da directory aziendali (emis.cn, maukerja.my). Azienda storica dal 1978. Sede non a Perlis. [DUPLICATO — vedi anche: 2026-10-01_07_Malesia_Kelantan_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -660,7 +653,6 @@
           <t>Dust Cone Hopper Systems Sdn Bhd</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Petaling Jaya, Selangor</t>
@@ -676,10 +668,9 @@
           <t>6011-16664030</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nessun sito ufficiale reperito, ma esistenza e contatti confermati da directory di settore (bulkinside.com, sgpgrid.com). Nicchia specifica, sede non a Perlis.</t>
+          <t>Nessun sito ufficiale reperito, ma esistenza e contatti confermati da directory di settore (bulkinside.com, sgpgrid.com). Nicchia specifica, sede non a Perlis. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -714,7 +705,6 @@
           <t>+603-8023 8250</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Grande multinazionale, esistenza e contatti confermati da fonti multiple. Sede regionale a Selangor, non a Perlis.</t>
@@ -722,7 +712,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -732,7 +722,6 @@
           <t>SINGUAN Blasting Sdn Bhd</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Shah Alam, Selangor</t>
@@ -743,8 +732,6 @@
           <t>Produzione/fornitura sand blasting machine, industrial dust collector custom-built, plastic deflashing machines, blasting media</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Produttore/fornitore di attrezzature (non cliente finale che eroga servizi di sabbiatura). Esistenza confermata da directory di settore (machinetools.com). Nessun contatto diretto reperito. Sede non a Perlis.</t>
@@ -752,7 +739,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -789,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Filiale malese di gruppo internazionale, confermata da fonti multiple coerenti coi dati forniti. Sede non a Perlis.</t>
+          <t>Filiale malese di gruppo internazionale, confermata da fonti multiple coerenti coi dati forniti. Sede non a Perlis. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
